--- a/resultados/aggregated_metrics.xlsx
+++ b/resultados/aggregated_metrics.xlsx
@@ -28,16 +28,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -48,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -56,21 +53,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,29 +428,29 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>f1-score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -474,14 +462,14 @@
         <v>0.8732394366197183</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8882521489971346</v>
+        <v>0.8882521489971347</v>
       </c>
       <c r="E2" t="n">
         <v>1065</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -493,14 +481,14 @@
         <v>0.9285714285714286</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9378757515030059</v>
+        <v>0.9378757515030061</v>
       </c>
       <c r="E3" t="n">
         <v>1008</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -519,7 +507,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -538,7 +526,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -550,14 +538,14 @@
         <v>0.9534180278281912</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9668711656441719</v>
+        <v>0.9668711656441717</v>
       </c>
       <c r="E6" t="n">
         <v>1653</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -576,7 +564,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -595,7 +583,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -607,14 +595,14 @@
         <v>0.6921182266009852</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7949080622347948</v>
+        <v>0.7949080622347949</v>
       </c>
       <c r="E9" t="n">
         <v>406</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -633,7 +621,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
@@ -652,7 +640,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>macro avg</t>
         </is>
@@ -671,7 +659,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>weighted avg</t>
         </is>
@@ -683,7 +671,7 @@
         <v>0.9320414847161572</v>
       </c>
       <c r="D13" t="n">
-        <v>0.931270331092208</v>
+        <v>0.9312703310922082</v>
       </c>
       <c r="E13" t="n">
         <v>10992</v>
@@ -704,29 +692,29 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>f1-score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -738,14 +726,14 @@
         <v>0.8798122065727699</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9026974951830442</v>
+        <v>0.9026974951830443</v>
       </c>
       <c r="E2" t="n">
         <v>1065</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -764,7 +752,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -776,14 +764,14 @@
         <v>0.9585714285714285</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9424157303370786</v>
+        <v>0.9424157303370787</v>
       </c>
       <c r="E4" t="n">
         <v>700</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -802,7 +790,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -821,7 +809,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -840,7 +828,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -852,14 +840,14 @@
         <v>0.8741258741258742</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8971291866028709</v>
+        <v>0.8971291866028708</v>
       </c>
       <c r="E8" t="n">
         <v>429</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -878,7 +866,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -897,7 +885,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
@@ -916,7 +904,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>macro avg</t>
         </is>
@@ -935,7 +923,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>weighted avg</t>
         </is>
@@ -968,29 +956,29 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>f1-score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1009,7 +997,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1021,14 +1009,14 @@
         <v>0.9375</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9324124321657621</v>
+        <v>0.9324124321657622</v>
       </c>
       <c r="E3" t="n">
         <v>1008</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1040,14 +1028,14 @@
         <v>0.9714285714285714</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9353507565337</v>
+        <v>0.9353507565337001</v>
       </c>
       <c r="E4" t="n">
         <v>700</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1066,7 +1054,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1078,14 +1066,14 @@
         <v>0.941923774954628</v>
       </c>
       <c r="D6" t="n">
-        <v>0.964385258593992</v>
+        <v>0.9643852585939919</v>
       </c>
       <c r="E6" t="n">
         <v>1653</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -1104,7 +1092,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -1123,7 +1111,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -1142,7 +1130,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1161,7 +1149,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
@@ -1180,7 +1168,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>macro avg</t>
         </is>
@@ -1199,7 +1187,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>weighted avg</t>
         </is>
@@ -1232,64 +1220,64 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>efficientnetv2b0</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>efficientnetv2b1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>efficientnetv2b2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>efficientnetv2b3</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>inceptionv3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>mobilenetv2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>mobilenetv3small</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>mobilenetv3large</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>nasnetmobile</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>resnet101v2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>resnet50</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
@@ -1329,7 +1317,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
@@ -1369,7 +1357,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
@@ -1409,13 +1397,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>f1_score</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.931270331092208</v>
+        <v>0.9312703310922082</v>
       </c>
       <c r="C5" t="n">
         <v>0.942032611597173</v>
@@ -1427,7 +1415,7 @@
         <v>0.940099622902514</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9250808977762469</v>
+        <v>0.9250808977762467</v>
       </c>
       <c r="G5" t="n">
         <v>0.9001083280163422</v>
@@ -1439,7 +1427,7 @@
         <v>0.9423294752256652</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9018985143074011</v>
+        <v>0.901898514307401</v>
       </c>
       <c r="K5" t="n">
         <v>0.9307187050709033</v>
@@ -1463,29 +1451,29 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>f1-score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1497,14 +1485,14 @@
         <v>0.888262910798122</v>
       </c>
       <c r="D2" t="n">
-        <v>0.89413988657845</v>
+        <v>0.8941398865784499</v>
       </c>
       <c r="E2" t="n">
         <v>1065</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1516,14 +1504,14 @@
         <v>0.9226190476190477</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9403437815975734</v>
+        <v>0.9403437815975733</v>
       </c>
       <c r="E3" t="n">
         <v>1008</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1542,7 +1530,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1554,14 +1542,14 @@
         <v>0.9232895646164478</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9411764705882354</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="E5" t="n">
         <v>1447</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1580,7 +1568,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -1592,14 +1580,14 @@
         <v>0.9563182527301092</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9511249030256012</v>
+        <v>0.9511249030256013</v>
       </c>
       <c r="E7" t="n">
         <v>641</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -1618,7 +1606,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -1637,7 +1625,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1649,14 +1637,14 @@
         <v>0.9698051056821301</v>
       </c>
       <c r="D10" t="n">
-        <v>0.949986555525679</v>
+        <v>0.9499865555256789</v>
       </c>
       <c r="E10" t="n">
         <v>3643</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
@@ -1675,7 +1663,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>macro avg</t>
         </is>
@@ -1687,14 +1675,14 @@
         <v>0.9254627120858595</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9320875118818608</v>
+        <v>0.9320875118818606</v>
       </c>
       <c r="E12" t="n">
         <v>10992</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>weighted avg</t>
         </is>
@@ -1727,29 +1715,29 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>f1-score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1768,7 +1756,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1787,7 +1775,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1799,14 +1787,14 @@
         <v>0.8228571428571428</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8875192604006165</v>
+        <v>0.8875192604006163</v>
       </c>
       <c r="E4" t="n">
         <v>700</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1825,7 +1813,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1837,14 +1825,14 @@
         <v>0.721113127646703</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8254847645429364</v>
+        <v>0.8254847645429363</v>
       </c>
       <c r="E6" t="n">
         <v>1653</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -1856,14 +1844,14 @@
         <v>0.8190327613104524</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8830950378469303</v>
+        <v>0.8830950378469302</v>
       </c>
       <c r="E7" t="n">
         <v>641</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -1882,7 +1870,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -1901,7 +1889,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1913,14 +1901,14 @@
         <v>0.96898160856437</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9471424738395493</v>
+        <v>0.9471424738395492</v>
       </c>
       <c r="E10" t="n">
         <v>3643</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
@@ -1939,7 +1927,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>macro avg</t>
         </is>
@@ -1958,7 +1946,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>weighted avg</t>
         </is>
@@ -1991,29 +1979,29 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>f1-score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2032,7 +2020,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2044,14 +2032,14 @@
         <v>0.9325396825396826</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9490156486622917</v>
+        <v>0.9490156486622918</v>
       </c>
       <c r="E3" t="n">
         <v>1008</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2070,7 +2058,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -2089,7 +2077,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -2101,14 +2089,14 @@
         <v>0.9534180278281912</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9647995102540556</v>
+        <v>0.9647995102540557</v>
       </c>
       <c r="E6" t="n">
         <v>1653</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -2120,14 +2108,14 @@
         <v>0.9641185647425897</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9611197511664076</v>
+        <v>0.9611197511664075</v>
       </c>
       <c r="E7" t="n">
         <v>641</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -2139,14 +2127,14 @@
         <v>0.9393939393939394</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9361207897793264</v>
+        <v>0.9361207897793263</v>
       </c>
       <c r="E8" t="n">
         <v>429</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -2165,7 +2153,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2184,7 +2172,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
@@ -2203,7 +2191,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>macro avg</t>
         </is>
@@ -2222,7 +2210,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>weighted avg</t>
         </is>
@@ -2255,29 +2243,29 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>f1-score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2296,7 +2284,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2308,14 +2296,14 @@
         <v>0.9156746031746031</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9337379868487609</v>
+        <v>0.9337379868487607</v>
       </c>
       <c r="E3" t="n">
         <v>1008</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2334,7 +2322,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -2346,14 +2334,14 @@
         <v>0.926744989633725</v>
       </c>
       <c r="D5" t="n">
-        <v>0.929636048526863</v>
+        <v>0.9296360485268631</v>
       </c>
       <c r="E5" t="n">
         <v>1447</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -2365,14 +2353,14 @@
         <v>0.9455535390199638</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9594843462246778</v>
+        <v>0.9594843462246777</v>
       </c>
       <c r="E6" t="n">
         <v>1653</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -2391,7 +2379,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -2403,14 +2391,14 @@
         <v>0.8717948717948718</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8904761904761905</v>
+        <v>0.8904761904761904</v>
       </c>
       <c r="E8" t="n">
         <v>429</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -2429,7 +2417,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2441,14 +2429,14 @@
         <v>0.9656876200933296</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9372585586785668</v>
+        <v>0.9372585586785667</v>
       </c>
       <c r="E10" t="n">
         <v>3643</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
@@ -2467,7 +2455,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>macro avg</t>
         </is>
@@ -2486,7 +2474,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>weighted avg</t>
         </is>
@@ -2498,7 +2486,7 @@
         <v>0.9259461426491994</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9250808977762469</v>
+        <v>0.9250808977762467</v>
       </c>
       <c r="E13" t="n">
         <v>10992</v>
@@ -2519,29 +2507,29 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>f1-score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2560,7 +2548,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2579,7 +2567,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2598,7 +2586,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -2617,7 +2605,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -2629,14 +2617,14 @@
         <v>0.9134906231094979</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9411031473979432</v>
+        <v>0.9411031473979433</v>
       </c>
       <c r="E6" t="n">
         <v>1653</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -2648,14 +2636,14 @@
         <v>0.9157566302652106</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9079659706109823</v>
+        <v>0.9079659706109822</v>
       </c>
       <c r="E7" t="n">
         <v>641</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -2667,14 +2655,14 @@
         <v>0.8461538461538461</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8531139835487662</v>
+        <v>0.8531139835487661</v>
       </c>
       <c r="E8" t="n">
         <v>429</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -2693,7 +2681,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2705,14 +2693,14 @@
         <v>0.9511391710129015</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9169092352474201</v>
+        <v>0.91690923524742</v>
       </c>
       <c r="E10" t="n">
         <v>3643</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
@@ -2731,7 +2719,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>macro avg</t>
         </is>
@@ -2750,7 +2738,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>weighted avg</t>
         </is>
@@ -2783,29 +2771,29 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>f1-score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2824,7 +2812,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2836,14 +2824,14 @@
         <v>0.9007936507936508</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9218274111675128</v>
+        <v>0.9218274111675127</v>
       </c>
       <c r="E3" t="n">
         <v>1008</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2862,7 +2850,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -2881,7 +2869,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -2893,14 +2881,14 @@
         <v>0.9497882637628554</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9631901840490799</v>
+        <v>0.9631901840490797</v>
       </c>
       <c r="E6" t="n">
         <v>1653</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -2919,7 +2907,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -2931,14 +2919,14 @@
         <v>0.8811188811188811</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8883666274970622</v>
+        <v>0.8883666274970623</v>
       </c>
       <c r="E8" t="n">
         <v>429</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -2950,14 +2938,14 @@
         <v>0.7364532019704434</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8102981029810299</v>
+        <v>0.8102981029810298</v>
       </c>
       <c r="E9" t="n">
         <v>406</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2976,7 +2964,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
@@ -2995,7 +2983,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>macro avg</t>
         </is>
@@ -3014,7 +3002,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>weighted avg</t>
         </is>
@@ -3047,29 +3035,29 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>f1-score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -3088,7 +3076,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3107,7 +3095,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -3119,14 +3107,14 @@
         <v>0.9842857142857143</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9602787456445994</v>
+        <v>0.9602787456445993</v>
       </c>
       <c r="E4" t="n">
         <v>700</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -3138,14 +3126,14 @@
         <v>0.9384934346924672</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9513134851138355</v>
+        <v>0.9513134851138354</v>
       </c>
       <c r="E5" t="n">
         <v>1447</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -3164,7 +3152,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -3176,14 +3164,14 @@
         <v>0.9500780031201248</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9478599221789884</v>
+        <v>0.9478599221789883</v>
       </c>
       <c r="E7" t="n">
         <v>641</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -3195,14 +3183,14 @@
         <v>0.8927738927738927</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9151732377538828</v>
+        <v>0.9151732377538829</v>
       </c>
       <c r="E8" t="n">
         <v>429</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -3221,7 +3209,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -3240,7 +3228,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
@@ -3259,7 +3247,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>macro avg</t>
         </is>
@@ -3278,7 +3266,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>weighted avg</t>
         </is>
@@ -3311,29 +3299,29 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>f1-score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -3352,7 +3340,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3371,7 +3359,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -3390,7 +3378,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -3409,7 +3397,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -3428,7 +3416,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -3447,7 +3435,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -3466,7 +3454,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -3485,7 +3473,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -3497,14 +3485,14 @@
         <v>0.9486686796596212</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9097130823901027</v>
+        <v>0.9097130823901026</v>
       </c>
       <c r="E10" t="n">
         <v>3643</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
@@ -3523,7 +3511,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>macro avg</t>
         </is>
@@ -3542,7 +3530,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>weighted avg</t>
         </is>
@@ -3554,7 +3542,7 @@
         <v>0.9026564774381368</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9018985143074011</v>
+        <v>0.901898514307401</v>
       </c>
       <c r="E13" t="n">
         <v>10992</v>
